--- a/endogineco2026/pre-congress/programacao-pre-congresso.xlsx
+++ b/endogineco2026/pre-congress/programacao-pre-congresso.xlsx
@@ -3,19 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="A Videocirugia na Oncol." sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Nutrição para pac. " sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="USG Endometriose " sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Sutura Laparoscópica " sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="PRÉ CONGRESSO (GERAL) " sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'A Videocirugia na Oncol.'!$A$1:$C$15</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Nutrição para pac. '!$A$1:$C$36</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'USG Endometriose '!$A$1:$C$22</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Sutura Laparoscópica '!$A$1:$C$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'PRÉ CONGRESSO (GERAL) '!$A$1:$C$78</definedName>
   </definedNames>
   <calcPr/>
   <extLst>
@@ -91,7 +85,7 @@
   </si>
   <si>
     <t xml:space="preserve">AUDITÓRIO B  - Curso Nutrição para pacientes com Endometriose 
-Coordenação:  Rosaura Santos - PE </t>
+Coordenação:  Rosaura Almeida  - PE </t>
   </si>
   <si>
     <t xml:space="preserve">13:30 - 13:40</t>
@@ -143,7 +137,7 @@
     <t xml:space="preserve">AULA 3</t>
   </si>
   <si>
-    <t xml:space="preserve">Nut. Adriana Soares</t>
+    <t xml:space="preserve">Nut. Nara Parente </t>
   </si>
   <si>
     <t xml:space="preserve">Nutrição Modulando a Inflamação</t>
@@ -380,10 +374,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11.000000"/>
-      <color indexed="64"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11.000000"/>
+      <color theme="10"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -838,314 +837,319 @@
       <diagonal style="none"/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="102">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="1" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="1" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="2" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf fontId="2" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="2" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf fontId="3" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf fontId="4" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="5" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="6" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="6" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="6" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="7" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="7" fillId="2" borderId="1" numFmtId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="7" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf fontId="4" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="7" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf fontId="7" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="5" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="5" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="5" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="4" fillId="5" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="5" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="6" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf fontId="4" fillId="6" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="7" fillId="7" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="7" fillId="6" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="2" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="6" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="8" fillId="7" borderId="7" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="6" fillId="2" borderId="1" numFmtId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="6" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="6" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="7" borderId="8" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="8" fillId="7" borderId="9" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="8" fillId="7" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="8" fillId="7" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="8" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="9" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="9" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="7" fillId="10" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="7" fillId="7" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="7" fillId="7" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="10" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="7" borderId="12" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf fontId="6" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="5" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="4" fillId="10" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="10" borderId="7" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="7" fillId="7" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf fontId="4" fillId="10" borderId="8" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="10" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="10" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="7" fillId="7" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="7" fillId="7" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="7" fillId="7" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="10" borderId="12" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="10" borderId="14" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="10" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="11" borderId="12" numFmtId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="8" fillId="7" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="5" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="8" fillId="7" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="6" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="6" fillId="7" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="6" fillId="6" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="1" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="6" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="7" fillId="7" borderId="7" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="4" fillId="11" borderId="15" numFmtId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="7" borderId="15" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="11" borderId="16" numFmtId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="7" borderId="16" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="11" borderId="17" numFmtId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="7" borderId="17" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="7" fillId="11" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="7" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="12" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="13" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="7" borderId="8" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="7" fillId="7" borderId="9" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="4" fillId="13" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="7" fillId="7" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="7" fillId="14" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="15" borderId="18" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="15" borderId="19" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="7" fillId="10" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="7" borderId="20" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="7" borderId="21" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="7" borderId="22" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="7" borderId="23" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="7" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="7" fillId="7" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="4" fillId="7" borderId="8" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="8" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="9" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="4" fillId="7" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="15" borderId="7" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf fontId="4" fillId="15" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf fontId="7" fillId="7" borderId="15" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="7" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf fontId="4" fillId="10" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="7" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="7" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="9" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="7" fillId="6" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="8" fillId="7" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="6" fillId="10" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="6" fillId="7" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="6" fillId="7" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="10" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="7" borderId="12" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf fontId="3" fillId="10" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="10" borderId="7" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="6" fillId="7" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf fontId="3" fillId="10" borderId="8" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="10" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="10" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="6" fillId="7" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="6" fillId="7" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="6" fillId="7" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="10" borderId="12" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="10" borderId="14" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="10" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="11" borderId="12" numFmtId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="7" fillId="7" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="7" fillId="16" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="16" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="16" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="7" fillId="6" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="7" fillId="6" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="6" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="6" borderId="7" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="7" fillId="10" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="7" fillId="17" borderId="5" numFmtId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="17" borderId="22" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="7" fillId="7" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="4" fillId="17" borderId="24" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="11" borderId="15" numFmtId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="7" borderId="15" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="11" borderId="16" numFmtId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="7" borderId="16" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="11" borderId="17" numFmtId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="7" borderId="17" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="6" fillId="11" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="6" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="12" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="13" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="7" fillId="6" borderId="5" numFmtId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="7" fillId="6" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="18" borderId="5" numFmtId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="18" borderId="22" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="13" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="4" fillId="18" borderId="24" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="6" fillId="14" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="15" borderId="18" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="15" borderId="19" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="6" fillId="10" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="7" borderId="20" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="7" borderId="21" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="7" borderId="22" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="7" borderId="23" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="7" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="8" fillId="7" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="7" borderId="8" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="7" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="15" borderId="7" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf fontId="3" fillId="15" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf fontId="6" fillId="7" borderId="15" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="7" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf fontId="3" fillId="10" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="7" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="6" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="6" fillId="6" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="7" fillId="7" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="6" fillId="16" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="16" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="16" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="6" fillId="6" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="6" fillId="6" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="6" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="6" borderId="7" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="6" fillId="10" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="6" fillId="17" borderId="5" numFmtId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="17" borderId="22" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="17" borderId="24" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="6" fillId="6" borderId="5" numFmtId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="6" fillId="6" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="18" borderId="5" numFmtId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="18" borderId="22" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="18" borderId="24" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="7" fillId="7" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="1" fillId="10" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="1" fillId="6" borderId="5" numFmtId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="1" fillId="6" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="2" fillId="10" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="2" fillId="6" borderId="5" numFmtId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="2" fillId="6" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperligação" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1166,114 +1170,14 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>44450</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>44450</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1409699" cy="314350"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Imagem 1"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip r:embed="rId1"/>
-        <a:srcRect l="0" t="21447" r="0" b="19043"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="44450" y="44450"/>
-          <a:ext cx="1409700" cy="314350"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>452968</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>77942</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="590549" cy="281350"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagem 2"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip r:embed="rId2"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1551518" y="77942"/>
-          <a:ext cx="590549" cy="281350"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>749301</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>33492</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="985232" cy="425450"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Imagem 3"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip r:embed="rId3"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="6915151" y="33492"/>
-          <a:ext cx="985232" cy="425450"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:w="http://schemas.openxmlformats.org/wordprocessingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
       <xdr:colOff>57150</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>44450</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1409699" cy="314350"/>
+    <xdr:ext cx="1409698" cy="314350"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Imagem 1"/>
+        <xdr:cNvPr id="14" name="Imagem 13"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1298,14 +1202,14 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>433918</xdr:colOff>
+      <xdr:colOff>402168</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>77942</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="590549" cy="281350"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagem 2"/>
+        <xdr:cNvPr id="15" name="Imagem 14"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
@@ -1316,7 +1220,7 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1532468" y="77942"/>
+          <a:off x="1500718" y="77942"/>
           <a:ext cx="590549" cy="281350"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1337,207 +1241,7 @@
     <xdr:ext cx="985232" cy="425450"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Imagem 3"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip r:embed="rId3"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="6915151" y="33492"/>
-          <a:ext cx="985232" cy="425450"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:w="http://schemas.openxmlformats.org/wordprocessingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>44450</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1409699" cy="314350"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Imagem 1"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip r:embed="rId1"/>
-        <a:srcRect l="0" t="21447" r="0" b="19043"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="38100" y="44450"/>
-          <a:ext cx="1409700" cy="314350"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>427568</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>77942</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="590549" cy="281350"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagem 2"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip r:embed="rId2"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1526118" y="77942"/>
-          <a:ext cx="590549" cy="281350"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>749301</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>33492</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="985232" cy="425450"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Imagem 3"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip r:embed="rId3"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="6915151" y="33492"/>
-          <a:ext cx="985232" cy="425450"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:w="http://schemas.openxmlformats.org/wordprocessingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>44450</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>44450</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1409699" cy="314350"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Imagem 1"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip r:embed="rId1"/>
-        <a:srcRect l="0" t="21447" r="0" b="19043"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="44450" y="44450"/>
-          <a:ext cx="1409700" cy="314350"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>421218</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>77942</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="590549" cy="281350"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagem 2"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip r:embed="rId2"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1519768" y="77942"/>
-          <a:ext cx="590549" cy="281350"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>749301</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>33492</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="985232" cy="425450"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Imagem 3"/>
+        <xdr:cNvPr id="16" name="Imagem 15"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -2195,812 +1899,630 @@
       <c r="C15" s="27"/>
       <c r="D15" s="21"/>
     </row>
+    <row r="16" s="21" customFormat="1" ht="35.149999999999999" customHeight="1">
+      <c r="A16" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="30"/>
+      <c r="D16" s="21"/>
+    </row>
+    <row r="17" s="21" customFormat="1" ht="30.75" customHeight="1">
+      <c r="A17" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="33"/>
+      <c r="D17" s="21"/>
+    </row>
+    <row r="18" s="21" customFormat="1" ht="25" customHeight="1">
+      <c r="A18" s="34" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="21"/>
+    </row>
+    <row r="19" s="21" customFormat="1" ht="25" customHeight="1">
+      <c r="A19" s="37"/>
+      <c r="B19" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="39"/>
+      <c r="D19" s="21"/>
+    </row>
+    <row r="20" s="21" customFormat="1" ht="25" customHeight="1">
+      <c r="A20" s="40"/>
+      <c r="B20" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="41"/>
+      <c r="D20" s="21"/>
+    </row>
+    <row r="21" s="21" customFormat="1" ht="25" customHeight="1">
+      <c r="A21" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="21"/>
+    </row>
+    <row r="22" s="21" customFormat="1" ht="25" customHeight="1">
+      <c r="A22" s="37"/>
+      <c r="B22" s="42" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" s="39"/>
+      <c r="D22" s="21"/>
+    </row>
+    <row r="23" s="21" customFormat="1" ht="25" customHeight="1">
+      <c r="A23" s="37"/>
+      <c r="B23" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="39"/>
+      <c r="D23" s="21"/>
+    </row>
+    <row r="24" s="21" customFormat="1" ht="25" customHeight="1">
+      <c r="A24" s="37"/>
+      <c r="B24" s="44" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="39"/>
+      <c r="D24" s="21"/>
+    </row>
+    <row r="25" s="21" customFormat="1" ht="25" customHeight="1">
+      <c r="A25" s="40"/>
+      <c r="B25" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" s="41"/>
+      <c r="D25" s="21"/>
+    </row>
+    <row r="26" s="21" customFormat="1" ht="25" customHeight="1">
+      <c r="A26" s="45" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="D26" s="21"/>
+    </row>
+    <row r="27" s="21" customFormat="1" ht="25" customHeight="1">
+      <c r="A27" s="46"/>
+      <c r="B27" s="44" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" s="46"/>
+      <c r="D27" s="21"/>
+    </row>
+    <row r="28" s="21" customFormat="1" ht="25" customHeight="1">
+      <c r="A28" s="46"/>
+      <c r="B28" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" s="46"/>
+      <c r="D28" s="21"/>
+    </row>
+    <row r="29" s="21" customFormat="1" ht="25" customHeight="1">
+      <c r="A29" s="46"/>
+      <c r="B29" s="44" t="s">
+        <v>40</v>
+      </c>
+      <c r="C29" s="46"/>
+      <c r="D29" s="21"/>
+    </row>
+    <row r="30" s="21" customFormat="1" ht="25" customHeight="1">
+      <c r="A30" s="47"/>
+      <c r="B30" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="C30" s="47"/>
+      <c r="D30" s="21"/>
+    </row>
+    <row r="31" s="21" customFormat="1" ht="25" customHeight="1">
+      <c r="A31" s="48" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="49" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="50"/>
+      <c r="D31" s="21"/>
+    </row>
+    <row r="32" s="21" customFormat="1" ht="25" customHeight="1">
+      <c r="A32" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32" s="52" t="s">
+        <v>45</v>
+      </c>
+      <c r="D32" s="21"/>
+    </row>
+    <row r="33" s="21" customFormat="1" ht="25" customHeight="1">
+      <c r="A33" s="53"/>
+      <c r="B33" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="C33" s="54"/>
+      <c r="D33" s="21"/>
+    </row>
+    <row r="34" s="21" customFormat="1" ht="25" customHeight="1">
+      <c r="A34" s="53"/>
+      <c r="B34" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="C34" s="54"/>
+      <c r="D34" s="21"/>
+    </row>
+    <row r="35" s="21" customFormat="1" ht="25" customHeight="1">
+      <c r="A35" s="53"/>
+      <c r="B35" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="C35" s="54"/>
+      <c r="D35" s="21"/>
+    </row>
+    <row r="36" s="21" customFormat="1" ht="25" customHeight="1">
+      <c r="A36" s="55"/>
+      <c r="B36" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="C36" s="56"/>
+      <c r="D36" s="21"/>
+    </row>
+    <row r="37" s="21" customFormat="1" ht="25" customHeight="1">
+      <c r="A37" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="B37" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="C37" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="D37" s="21"/>
+    </row>
+    <row r="38" s="21" customFormat="1" ht="25" customHeight="1">
+      <c r="A38" s="53"/>
+      <c r="B38" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="C38" s="54"/>
+      <c r="D38" s="21"/>
+    </row>
+    <row r="39" s="21" customFormat="1" ht="25" customHeight="1">
+      <c r="A39" s="53"/>
+      <c r="B39" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C39" s="54"/>
+      <c r="D39" s="21"/>
+    </row>
+    <row r="40" s="21" customFormat="1" ht="25" customHeight="1">
+      <c r="A40" s="53"/>
+      <c r="B40" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C40" s="54"/>
+      <c r="D40" s="21"/>
+    </row>
+    <row r="41" s="21" customFormat="1" ht="25" customHeight="1">
+      <c r="A41" s="55"/>
+      <c r="B41" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="C41" s="56"/>
+      <c r="D41" s="21"/>
+    </row>
+    <row r="42" s="21" customFormat="1" ht="25" customHeight="1">
+      <c r="A42" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="B42" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="C42" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="D42" s="21"/>
+    </row>
+    <row r="43" s="21" customFormat="1" ht="25" customHeight="1">
+      <c r="A43" s="53"/>
+      <c r="B43" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="C43" s="54"/>
+      <c r="D43" s="21"/>
+    </row>
+    <row r="44" s="21" customFormat="1" ht="25" customHeight="1">
+      <c r="A44" s="53"/>
+      <c r="B44" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="C44" s="54"/>
+      <c r="D44" s="21"/>
+    </row>
+    <row r="45" s="21" customFormat="1" ht="25" customHeight="1">
+      <c r="A45" s="53"/>
+      <c r="B45" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="C45" s="54"/>
+      <c r="D45" s="21"/>
+    </row>
+    <row r="46" s="21" customFormat="1" ht="28" customHeight="1">
+      <c r="A46" s="55"/>
+      <c r="B46" s="57" t="s">
+        <v>63</v>
+      </c>
+      <c r="C46" s="56"/>
+      <c r="D46" s="21"/>
+    </row>
+    <row r="47" s="58" customFormat="1" ht="41.25" customHeight="1">
+      <c r="A47" s="59" t="s">
+        <v>64</v>
+      </c>
+      <c r="B47" s="60" t="s">
+        <v>65</v>
+      </c>
+      <c r="C47" s="61"/>
+      <c r="D47" s="58"/>
+    </row>
+    <row r="48" s="58" customFormat="1" ht="24" customHeight="1">
+      <c r="A48" s="62" t="s">
+        <v>66</v>
+      </c>
+      <c r="B48" s="63" t="s">
+        <v>67</v>
+      </c>
+      <c r="C48" s="64"/>
+      <c r="D48" s="58"/>
+    </row>
+    <row r="49" s="58" customFormat="1" ht="24" customHeight="1">
+      <c r="A49" s="65"/>
+      <c r="B49" s="66" t="s">
+        <v>68</v>
+      </c>
+      <c r="C49" s="67"/>
+      <c r="D49" s="58"/>
+    </row>
+    <row r="50" s="58" customFormat="1" ht="24" customHeight="1">
+      <c r="A50" s="65"/>
+      <c r="B50" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="C50" s="69"/>
+      <c r="D50" s="58"/>
+    </row>
+    <row r="51" s="58" customFormat="1" ht="27.75" customHeight="1">
+      <c r="A51" s="65"/>
+      <c r="B51" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="C51" s="70"/>
+      <c r="D51" s="58"/>
+    </row>
+    <row r="52" s="58" customFormat="1" ht="27.75" customHeight="1">
+      <c r="A52" s="65"/>
+      <c r="B52" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="C52" s="71"/>
+      <c r="D52" s="58"/>
+    </row>
+    <row r="53" s="58" customFormat="1" ht="24" customHeight="1">
+      <c r="A53" s="65"/>
+      <c r="B53" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="C53" s="72"/>
+      <c r="D53" s="58"/>
+    </row>
+    <row r="54" s="58" customFormat="1" ht="24" customHeight="1">
+      <c r="A54" s="62" t="s">
+        <v>73</v>
+      </c>
+      <c r="B54" s="73" t="s">
+        <v>74</v>
+      </c>
+      <c r="C54" s="74"/>
+      <c r="D54" s="58"/>
+    </row>
+    <row r="55" s="58" customFormat="1" ht="30" customHeight="1">
+      <c r="A55" s="65"/>
+      <c r="B55" s="75" t="s">
+        <v>75</v>
+      </c>
+      <c r="C55" s="76"/>
+      <c r="D55" s="58"/>
+    </row>
+    <row r="56" s="58" customFormat="1" ht="30" customHeight="1">
+      <c r="A56" s="77"/>
+      <c r="B56" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="C56" s="78"/>
+      <c r="D56" s="58"/>
+    </row>
+    <row r="57" s="79" customFormat="1" ht="28" customHeight="1">
+      <c r="A57" s="80" t="s">
+        <v>12</v>
+      </c>
+      <c r="B57" s="81" t="s">
+        <v>13</v>
+      </c>
+      <c r="C57" s="26"/>
+    </row>
+    <row r="58" s="79" customFormat="1" ht="24" customHeight="1">
+      <c r="A58" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="B58" s="83" t="s">
+        <v>78</v>
+      </c>
+      <c r="C58" s="84"/>
+    </row>
+    <row r="59" s="79" customFormat="1" ht="24" customHeight="1">
+      <c r="A59" s="85"/>
+      <c r="B59" s="86" t="s">
+        <v>79</v>
+      </c>
+      <c r="C59" s="87"/>
+    </row>
+    <row r="60" s="79" customFormat="1" ht="24" customHeight="1">
+      <c r="A60" s="80"/>
+      <c r="B60" s="88" t="s">
+        <v>80</v>
+      </c>
+      <c r="C60" s="87"/>
+    </row>
+    <row r="61" s="79" customFormat="1" ht="30" customHeight="1">
+      <c r="A61" s="85"/>
+      <c r="B61" s="86" t="s">
+        <v>81</v>
+      </c>
+      <c r="C61" s="87"/>
+    </row>
+    <row r="62" s="79" customFormat="1" ht="30" customHeight="1">
+      <c r="A62" s="85"/>
+      <c r="B62" s="86" t="s">
+        <v>82</v>
+      </c>
+      <c r="C62" s="87"/>
+    </row>
+    <row r="63" s="79" customFormat="1" ht="30" customHeight="1">
+      <c r="A63" s="85"/>
+      <c r="B63" s="86" t="s">
+        <v>83</v>
+      </c>
+      <c r="C63" s="87"/>
+    </row>
+    <row r="64" s="89" customFormat="1" ht="35.149999999999999" customHeight="1">
+      <c r="A64" s="90" t="s">
+        <v>84</v>
+      </c>
+      <c r="B64" s="91" t="s">
+        <v>85</v>
+      </c>
+      <c r="C64" s="92"/>
+      <c r="D64" s="89"/>
+    </row>
+    <row r="65" s="89" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A65" s="93" t="s">
+        <v>86</v>
+      </c>
+      <c r="B65" s="94" t="s">
+        <v>87</v>
+      </c>
+      <c r="C65" s="94" t="s">
+        <v>88</v>
+      </c>
+      <c r="D65" s="89"/>
+    </row>
+    <row r="66" s="89" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A66" s="93" t="s">
+        <v>89</v>
+      </c>
+      <c r="B66" s="94" t="s">
+        <v>90</v>
+      </c>
+      <c r="C66" s="94" t="s">
+        <v>91</v>
+      </c>
+      <c r="D66" s="89"/>
+    </row>
+    <row r="67" s="89" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A67" s="93" t="s">
+        <v>92</v>
+      </c>
+      <c r="B67" s="94" t="s">
+        <v>93</v>
+      </c>
+      <c r="C67" s="94" t="s">
+        <v>94</v>
+      </c>
+      <c r="D67" s="89"/>
+    </row>
+    <row r="68" s="89" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A68" s="95" t="s">
+        <v>95</v>
+      </c>
+      <c r="B68" s="96" t="s">
+        <v>96</v>
+      </c>
+      <c r="C68" s="97"/>
+      <c r="D68" s="89"/>
+    </row>
+    <row r="69" s="89" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A69" s="93" t="s">
+        <v>97</v>
+      </c>
+      <c r="B69" s="94" t="s">
+        <v>98</v>
+      </c>
+      <c r="C69" s="94"/>
+      <c r="D69" s="89"/>
+    </row>
+    <row r="70" s="89" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A70" s="93" t="s">
+        <v>99</v>
+      </c>
+      <c r="B70" s="94" t="s">
+        <v>100</v>
+      </c>
+      <c r="C70" s="94"/>
+      <c r="D70" s="89"/>
+    </row>
+    <row r="71" s="89" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A71" s="93" t="s">
+        <v>101</v>
+      </c>
+      <c r="B71" s="94" t="s">
+        <v>102</v>
+      </c>
+      <c r="C71" s="94"/>
+      <c r="D71" s="89"/>
+    </row>
+    <row r="72" s="89" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A72" s="93" t="s">
+        <v>12</v>
+      </c>
+      <c r="B72" s="98" t="s">
+        <v>13</v>
+      </c>
+      <c r="C72" s="27"/>
+      <c r="D72" s="89"/>
+    </row>
+    <row r="73" s="89" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A73" s="93" t="s">
+        <v>103</v>
+      </c>
+      <c r="B73" s="94" t="s">
+        <v>104</v>
+      </c>
+      <c r="C73" s="94" t="s">
+        <v>88</v>
+      </c>
+      <c r="D73" s="89"/>
+    </row>
+    <row r="74" s="89" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A74" s="93" t="s">
+        <v>105</v>
+      </c>
+      <c r="B74" s="94" t="s">
+        <v>106</v>
+      </c>
+      <c r="C74" s="94" t="s">
+        <v>91</v>
+      </c>
+      <c r="D74" s="89"/>
+    </row>
+    <row r="75" s="89" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A75" s="93" t="s">
+        <v>107</v>
+      </c>
+      <c r="B75" s="86" t="s">
+        <v>96</v>
+      </c>
+      <c r="C75" s="94" t="s">
+        <v>94</v>
+      </c>
+      <c r="D75" s="89"/>
+    </row>
+    <row r="76" s="89" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A76" s="93" t="s">
+        <v>108</v>
+      </c>
+      <c r="B76" s="94" t="s">
+        <v>109</v>
+      </c>
+      <c r="C76" s="94"/>
+      <c r="D76" s="89"/>
+    </row>
+    <row r="77" s="89" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A77" s="93" t="s">
+        <v>110</v>
+      </c>
+      <c r="B77" s="94" t="s">
+        <v>111</v>
+      </c>
+      <c r="C77" s="94"/>
+      <c r="D77" s="89"/>
+    </row>
+    <row r="78" s="89" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A78" s="93" t="s">
+        <v>112</v>
+      </c>
+      <c r="B78" s="94" t="s">
+        <v>113</v>
+      </c>
+      <c r="C78" s="94"/>
+      <c r="D78" s="89"/>
+    </row>
+    <row r="79" s="99" customFormat="1" ht="25" customHeight="1">
+      <c r="A79" s="100"/>
+      <c r="B79" s="101"/>
+      <c r="C79" s="101"/>
+      <c r="D79" s="99"/>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="29">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="A21:A25"/>
+    <mergeCell ref="C21:C25"/>
+    <mergeCell ref="A26:A30"/>
+    <mergeCell ref="C26:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A32:A36"/>
+    <mergeCell ref="C32:C36"/>
+    <mergeCell ref="A37:A41"/>
+    <mergeCell ref="C37:C41"/>
+    <mergeCell ref="A42:A46"/>
+    <mergeCell ref="C42:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B72:C72"/>
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.39370078740157477" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="68" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="0" verticalDpi="0" copies="1"/>
   <headerFooter/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultColWidth="10.26953125" defaultRowHeight="14.25"/>
-  <cols>
-    <col customWidth="1" min="1" max="1" style="2" width="15.7265625"/>
-    <col customWidth="1" min="2" max="2" style="1" width="72.54296875"/>
-    <col customWidth="1" min="3" max="3" style="1" width="29.26953125"/>
-    <col min="4" max="16384" style="1" width="10.26953125"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="39.649999999999999" customHeight="1">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-    </row>
-    <row r="2" s="5" customFormat="1" ht="16.5">
-      <c r="A2" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" s="5" customFormat="1" ht="15.5">
-      <c r="A3" s="6"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="8"/>
-    </row>
-    <row r="4" s="9" customFormat="1" ht="25" customHeight="1">
-      <c r="A4" s="10">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="11"/>
-    </row>
-    <row r="5" s="12" customFormat="1" ht="28" customHeight="1">
-      <c r="A5" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="14"/>
-    </row>
-    <row r="6" s="21" customFormat="1" ht="35.149999999999999" customHeight="1">
-      <c r="A6" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="30"/>
-      <c r="D6" s="21"/>
-    </row>
-    <row r="7" s="21" customFormat="1" ht="30.75" customHeight="1">
-      <c r="A7" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="33"/>
-      <c r="D7" s="21"/>
-    </row>
-    <row r="8" s="21" customFormat="1" ht="25" customHeight="1">
-      <c r="A8" s="34" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="21"/>
-    </row>
-    <row r="9" s="21" customFormat="1" ht="25" customHeight="1">
-      <c r="A9" s="37"/>
-      <c r="B9" s="38" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="39"/>
-      <c r="D9" s="21"/>
-    </row>
-    <row r="10" s="21" customFormat="1" ht="25" customHeight="1">
-      <c r="A10" s="40"/>
-      <c r="B10" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="41"/>
-      <c r="D10" s="21"/>
-    </row>
-    <row r="11" s="21" customFormat="1" ht="25" customHeight="1">
-      <c r="A11" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="21"/>
-    </row>
-    <row r="12" s="21" customFormat="1" ht="25" customHeight="1">
-      <c r="A12" s="37"/>
-      <c r="B12" s="42" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="39"/>
-      <c r="D12" s="21"/>
-    </row>
-    <row r="13" s="21" customFormat="1" ht="25" customHeight="1">
-      <c r="A13" s="37"/>
-      <c r="B13" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="39"/>
-      <c r="D13" s="21"/>
-    </row>
-    <row r="14" s="21" customFormat="1" ht="25" customHeight="1">
-      <c r="A14" s="37"/>
-      <c r="B14" s="44" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="39"/>
-      <c r="D14" s="21"/>
-    </row>
-    <row r="15" s="21" customFormat="1" ht="25" customHeight="1">
-      <c r="A15" s="40"/>
-      <c r="B15" s="44" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" s="41"/>
-      <c r="D15" s="21"/>
-    </row>
-    <row r="16" s="21" customFormat="1" ht="25" customHeight="1">
-      <c r="A16" s="45" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="35" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" s="45" t="s">
-        <v>37</v>
-      </c>
-      <c r="D16" s="21"/>
-    </row>
-    <row r="17" s="21" customFormat="1" ht="25" customHeight="1">
-      <c r="A17" s="46"/>
-      <c r="B17" s="44" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17" s="46"/>
-      <c r="D17" s="21"/>
-    </row>
-    <row r="18" s="21" customFormat="1" ht="25" customHeight="1">
-      <c r="A18" s="46"/>
-      <c r="B18" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="C18" s="46"/>
-      <c r="D18" s="21"/>
-    </row>
-    <row r="19" s="21" customFormat="1" ht="25" customHeight="1">
-      <c r="A19" s="46"/>
-      <c r="B19" s="44" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19" s="46"/>
-      <c r="D19" s="21"/>
-    </row>
-    <row r="20" s="21" customFormat="1" ht="25" customHeight="1">
-      <c r="A20" s="47"/>
-      <c r="B20" s="44" t="s">
-        <v>41</v>
-      </c>
-      <c r="C20" s="47"/>
-      <c r="D20" s="21"/>
-    </row>
-    <row r="21" s="21" customFormat="1" ht="25" customHeight="1">
-      <c r="A21" s="48" t="s">
-        <v>42</v>
-      </c>
-      <c r="B21" s="49" t="s">
-        <v>13</v>
-      </c>
-      <c r="C21" s="50"/>
-      <c r="D21" s="21"/>
-    </row>
-    <row r="22" s="21" customFormat="1" ht="25" customHeight="1">
-      <c r="A22" s="51" t="s">
-        <v>43</v>
-      </c>
-      <c r="B22" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" s="52" t="s">
-        <v>45</v>
-      </c>
-      <c r="D22" s="21"/>
-    </row>
-    <row r="23" s="21" customFormat="1" ht="25" customHeight="1">
-      <c r="A23" s="53"/>
-      <c r="B23" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23" s="54"/>
-      <c r="D23" s="21"/>
-    </row>
-    <row r="24" s="21" customFormat="1" ht="25" customHeight="1">
-      <c r="A24" s="53"/>
-      <c r="B24" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="C24" s="54"/>
-      <c r="D24" s="21"/>
-    </row>
-    <row r="25" s="21" customFormat="1" ht="25" customHeight="1">
-      <c r="A25" s="53"/>
-      <c r="B25" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="C25" s="54"/>
-      <c r="D25" s="21"/>
-    </row>
-    <row r="26" s="21" customFormat="1" ht="25" customHeight="1">
-      <c r="A26" s="55"/>
-      <c r="B26" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="C26" s="56"/>
-      <c r="D26" s="21"/>
-    </row>
-    <row r="27" s="21" customFormat="1" ht="25" customHeight="1">
-      <c r="A27" s="51" t="s">
-        <v>50</v>
-      </c>
-      <c r="B27" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="C27" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="D27" s="21"/>
-    </row>
-    <row r="28" s="21" customFormat="1" ht="25" customHeight="1">
-      <c r="A28" s="53"/>
-      <c r="B28" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="C28" s="54"/>
-      <c r="D28" s="21"/>
-    </row>
-    <row r="29" s="21" customFormat="1" ht="25" customHeight="1">
-      <c r="A29" s="53"/>
-      <c r="B29" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C29" s="54"/>
-      <c r="D29" s="21"/>
-    </row>
-    <row r="30" s="21" customFormat="1" ht="25" customHeight="1">
-      <c r="A30" s="53"/>
-      <c r="B30" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="C30" s="54"/>
-      <c r="D30" s="21"/>
-    </row>
-    <row r="31" s="21" customFormat="1" ht="25" customHeight="1">
-      <c r="A31" s="55"/>
-      <c r="B31" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="C31" s="56"/>
-      <c r="D31" s="21"/>
-    </row>
-    <row r="32" s="21" customFormat="1" ht="25" customHeight="1">
-      <c r="A32" s="51" t="s">
-        <v>57</v>
-      </c>
-      <c r="B32" s="35" t="s">
-        <v>58</v>
-      </c>
-      <c r="C32" s="52" t="s">
-        <v>59</v>
-      </c>
-      <c r="D32" s="21"/>
-    </row>
-    <row r="33" s="21" customFormat="1" ht="25" customHeight="1">
-      <c r="A33" s="53"/>
-      <c r="B33" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="C33" s="54"/>
-      <c r="D33" s="21"/>
-    </row>
-    <row r="34" s="21" customFormat="1" ht="25" customHeight="1">
-      <c r="A34" s="53"/>
-      <c r="B34" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="C34" s="54"/>
-      <c r="D34" s="21"/>
-    </row>
-    <row r="35" s="21" customFormat="1" ht="25" customHeight="1">
-      <c r="A35" s="53"/>
-      <c r="B35" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="C35" s="54"/>
-      <c r="D35" s="21"/>
-    </row>
-    <row r="36" s="21" customFormat="1" ht="28" customHeight="1">
-      <c r="A36" s="55"/>
-      <c r="B36" s="57" t="s">
-        <v>63</v>
-      </c>
-      <c r="C36" s="56"/>
-      <c r="D36" s="21"/>
-    </row>
-  </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="A11:A15"/>
-    <mergeCell ref="C11:C15"/>
-    <mergeCell ref="A16:A20"/>
-    <mergeCell ref="C16:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="A22:A26"/>
-    <mergeCell ref="C22:C26"/>
-    <mergeCell ref="A27:A31"/>
-    <mergeCell ref="C27:C31"/>
-    <mergeCell ref="A32:A36"/>
-    <mergeCell ref="C32:C36"/>
-  </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.39370078740157477" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="68" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="0" verticalDpi="0" copies="1"/>
-  <headerFooter/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultColWidth="10.26953125" defaultRowHeight="14.25"/>
-  <cols>
-    <col customWidth="1" min="1" max="1" style="2" width="15.7265625"/>
-    <col customWidth="1" min="2" max="2" style="1" width="72.54296875"/>
-    <col customWidth="1" min="3" max="3" style="1" width="29.26953125"/>
-    <col min="4" max="16384" style="1" width="10.26953125"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="39.649999999999999" customHeight="1">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-    </row>
-    <row r="2" s="5" customFormat="1" ht="16.5">
-      <c r="A2" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" s="5" customFormat="1" ht="15.5">
-      <c r="A3" s="6"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="8"/>
-    </row>
-    <row r="4" s="9" customFormat="1" ht="25" customHeight="1">
-      <c r="A4" s="10">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="11"/>
-    </row>
-    <row r="5" s="12" customFormat="1" ht="28" customHeight="1">
-      <c r="A5" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="14"/>
-    </row>
-    <row r="6" s="58" customFormat="1" ht="41.25" customHeight="1">
-      <c r="A6" s="59" t="s">
-        <v>64</v>
-      </c>
-      <c r="B6" s="60" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" s="61"/>
-      <c r="D6" s="58"/>
-    </row>
-    <row r="7" s="58" customFormat="1" ht="24" customHeight="1">
-      <c r="A7" s="62" t="s">
-        <v>66</v>
-      </c>
-      <c r="B7" s="63" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" s="64"/>
-      <c r="D7" s="58"/>
-    </row>
-    <row r="8" s="58" customFormat="1" ht="24" customHeight="1">
-      <c r="A8" s="65"/>
-      <c r="B8" s="66" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" s="67"/>
-      <c r="D8" s="58"/>
-    </row>
-    <row r="9" s="58" customFormat="1" ht="24" customHeight="1">
-      <c r="A9" s="65"/>
-      <c r="B9" s="68" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" s="69"/>
-      <c r="D9" s="58"/>
-    </row>
-    <row r="10" s="58" customFormat="1" ht="27.75" customHeight="1">
-      <c r="A10" s="65"/>
-      <c r="B10" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" s="70"/>
-      <c r="D10" s="58"/>
-    </row>
-    <row r="11" s="58" customFormat="1" ht="27.75" customHeight="1">
-      <c r="A11" s="65"/>
-      <c r="B11" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" s="71"/>
-      <c r="D11" s="58"/>
-    </row>
-    <row r="12" s="58" customFormat="1" ht="24" customHeight="1">
-      <c r="A12" s="65"/>
-      <c r="B12" s="42" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" s="72"/>
-      <c r="D12" s="58"/>
-    </row>
-    <row r="13" s="58" customFormat="1" ht="24" customHeight="1">
-      <c r="A13" s="62" t="s">
-        <v>73</v>
-      </c>
-      <c r="B13" s="73" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" s="74"/>
-      <c r="D13" s="58"/>
-    </row>
-    <row r="14" s="58" customFormat="1" ht="30" customHeight="1">
-      <c r="A14" s="65"/>
-      <c r="B14" s="75" t="s">
-        <v>75</v>
-      </c>
-      <c r="C14" s="76"/>
-      <c r="D14" s="58"/>
-    </row>
-    <row r="15" s="58" customFormat="1" ht="30" customHeight="1">
-      <c r="A15" s="77"/>
-      <c r="B15" s="42" t="s">
-        <v>76</v>
-      </c>
-      <c r="C15" s="78"/>
-      <c r="D15" s="58"/>
-    </row>
-    <row r="16" s="79" customFormat="1" ht="28" customHeight="1">
-      <c r="A16" s="80" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" s="81" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" s="26"/>
-    </row>
-    <row r="17" s="79" customFormat="1" ht="24" customHeight="1">
-      <c r="A17" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="B17" s="83" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17" s="84"/>
-    </row>
-    <row r="18" s="79" customFormat="1" ht="24" customHeight="1">
-      <c r="A18" s="85"/>
-      <c r="B18" s="86" t="s">
-        <v>79</v>
-      </c>
-      <c r="C18" s="87"/>
-    </row>
-    <row r="19" s="79" customFormat="1" ht="24" customHeight="1">
-      <c r="A19" s="80"/>
-      <c r="B19" s="88" t="s">
-        <v>80</v>
-      </c>
-      <c r="C19" s="87"/>
-    </row>
-    <row r="20" s="79" customFormat="1" ht="30" customHeight="1">
-      <c r="A20" s="85"/>
-      <c r="B20" s="86" t="s">
-        <v>81</v>
-      </c>
-      <c r="C20" s="87"/>
-    </row>
-    <row r="21" s="79" customFormat="1" ht="30" customHeight="1">
-      <c r="A21" s="85"/>
-      <c r="B21" s="86" t="s">
-        <v>82</v>
-      </c>
-      <c r="C21" s="87"/>
-    </row>
-    <row r="22" s="79" customFormat="1" ht="30" customHeight="1">
-      <c r="A22" s="85"/>
-      <c r="B22" s="86" t="s">
-        <v>83</v>
-      </c>
-      <c r="C22" s="87"/>
-    </row>
-  </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B19:C19"/>
-  </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.39370078740157477" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="68" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="0" verticalDpi="0" copies="1"/>
-  <headerFooter/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultColWidth="10.26953125" defaultRowHeight="14.25"/>
-  <cols>
-    <col customWidth="1" min="1" max="1" style="2" width="15.7265625"/>
-    <col customWidth="1" min="2" max="2" style="1" width="72.54296875"/>
-    <col customWidth="1" min="3" max="3" style="1" width="29.26953125"/>
-    <col min="4" max="16384" style="1" width="10.26953125"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="39.649999999999999" customHeight="1">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-    </row>
-    <row r="2" s="5" customFormat="1" ht="16.5">
-      <c r="A2" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" s="5" customFormat="1" ht="15.5">
-      <c r="A3" s="6"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="8"/>
-    </row>
-    <row r="4" s="9" customFormat="1" ht="25" customHeight="1">
-      <c r="A4" s="10">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="11"/>
-    </row>
-    <row r="5" s="12" customFormat="1" ht="28" customHeight="1">
-      <c r="A5" s="13"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-    </row>
-    <row r="6" s="89" customFormat="1" ht="35.149999999999999" customHeight="1">
-      <c r="A6" s="90" t="s">
-        <v>84</v>
-      </c>
-      <c r="B6" s="91" t="s">
-        <v>85</v>
-      </c>
-      <c r="C6" s="92"/>
-      <c r="D6" s="89"/>
-    </row>
-    <row r="7" s="89" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A7" s="93" t="s">
-        <v>86</v>
-      </c>
-      <c r="B7" s="94" t="s">
-        <v>87</v>
-      </c>
-      <c r="C7" s="94" t="s">
-        <v>88</v>
-      </c>
-      <c r="D7" s="89"/>
-    </row>
-    <row r="8" s="89" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A8" s="93" t="s">
-        <v>89</v>
-      </c>
-      <c r="B8" s="94" t="s">
-        <v>90</v>
-      </c>
-      <c r="C8" s="94" t="s">
-        <v>91</v>
-      </c>
-      <c r="D8" s="89"/>
-    </row>
-    <row r="9" s="89" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A9" s="93" t="s">
-        <v>92</v>
-      </c>
-      <c r="B9" s="94" t="s">
-        <v>93</v>
-      </c>
-      <c r="C9" s="94" t="s">
-        <v>94</v>
-      </c>
-      <c r="D9" s="89"/>
-    </row>
-    <row r="10" s="89" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A10" s="95" t="s">
-        <v>95</v>
-      </c>
-      <c r="B10" s="96" t="s">
-        <v>96</v>
-      </c>
-      <c r="C10" s="97"/>
-      <c r="D10" s="89"/>
-    </row>
-    <row r="11" s="89" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A11" s="93" t="s">
-        <v>97</v>
-      </c>
-      <c r="B11" s="94" t="s">
-        <v>98</v>
-      </c>
-      <c r="C11" s="94"/>
-      <c r="D11" s="89"/>
-    </row>
-    <row r="12" s="89" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A12" s="93" t="s">
-        <v>99</v>
-      </c>
-      <c r="B12" s="94" t="s">
-        <v>100</v>
-      </c>
-      <c r="C12" s="94"/>
-      <c r="D12" s="89"/>
-    </row>
-    <row r="13" s="89" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A13" s="93" t="s">
-        <v>101</v>
-      </c>
-      <c r="B13" s="94" t="s">
-        <v>102</v>
-      </c>
-      <c r="C13" s="94"/>
-      <c r="D13" s="89"/>
-    </row>
-    <row r="14" s="89" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A14" s="93" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="98" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" s="27"/>
-      <c r="D14" s="89"/>
-    </row>
-    <row r="15" s="89" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A15" s="93" t="s">
-        <v>103</v>
-      </c>
-      <c r="B15" s="94" t="s">
-        <v>104</v>
-      </c>
-      <c r="C15" s="94" t="s">
-        <v>88</v>
-      </c>
-      <c r="D15" s="89"/>
-    </row>
-    <row r="16" s="89" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A16" s="93" t="s">
-        <v>105</v>
-      </c>
-      <c r="B16" s="94" t="s">
-        <v>106</v>
-      </c>
-      <c r="C16" s="94" t="s">
-        <v>91</v>
-      </c>
-      <c r="D16" s="89"/>
-    </row>
-    <row r="17" s="89" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A17" s="93" t="s">
-        <v>107</v>
-      </c>
-      <c r="B17" s="86" t="s">
-        <v>96</v>
-      </c>
-      <c r="C17" s="94" t="s">
-        <v>94</v>
-      </c>
-      <c r="D17" s="89"/>
-    </row>
-    <row r="18" s="89" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A18" s="93" t="s">
-        <v>108</v>
-      </c>
-      <c r="B18" s="94" t="s">
-        <v>109</v>
-      </c>
-      <c r="C18" s="94"/>
-      <c r="D18" s="89"/>
-    </row>
-    <row r="19" s="89" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A19" s="93" t="s">
-        <v>110</v>
-      </c>
-      <c r="B19" s="94" t="s">
-        <v>111</v>
-      </c>
-      <c r="C19" s="94"/>
-      <c r="D19" s="89"/>
-    </row>
-    <row r="20" s="89" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A20" s="93" t="s">
-        <v>112</v>
-      </c>
-      <c r="B20" s="94" t="s">
-        <v>113</v>
-      </c>
-      <c r="C20" s="94"/>
-      <c r="D20" s="89"/>
-    </row>
-    <row r="21" s="99" customFormat="1" ht="25" customHeight="1">
-      <c r="A21" s="100"/>
-      <c r="B21" s="101"/>
-      <c r="C21" s="101"/>
-      <c r="D21" s="99"/>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B14:C14"/>
-  </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.39370078740157477" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="68" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="0" verticalDpi="0" copies="1"/>
-  <headerFooter/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="46" man="1" max="2"/>
+  </rowBreaks>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/endogineco2026/pre-congress/programacao-pre-congresso.xlsx
+++ b/endogineco2026/pre-congress/programacao-pre-congresso.xlsx
@@ -9,7 +9,7 @@
     <sheet name="PRÉ CONGRESSO (GERAL) " sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'PRÉ CONGRESSO (GERAL) '!$A$1:$C$78</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'PRÉ CONGRESSO (GERAL) '!$A$1:$C$79</definedName>
   </definedNames>
   <calcPr/>
   <extLst>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="117">
   <si>
     <t xml:space="preserve">PRÉ CONGRESSO ENDOGINECO 2026 </t>
   </si>
@@ -279,92 +279,107 @@
     <t xml:space="preserve">O que há de Novo na Literatura Mundial: As evidências científicas e diretrizes internacionais mais recentes que estão mudando a conduta na endometriose profunda.</t>
   </si>
   <si>
-    <t xml:space="preserve">12:30 - 19:00</t>
+    <t xml:space="preserve">12:00 - 19:00</t>
   </si>
   <si>
     <t xml:space="preserve">FOYER - Curso de Sutura Dry Lab em sutura Endoscópica 
 Coordenação: Guilherme Zanluchi - SP</t>
   </si>
   <si>
-    <t xml:space="preserve">12:30 - 13:00 </t>
+    <t xml:space="preserve">12:00 - 12:30</t>
   </si>
   <si>
     <t xml:space="preserve">Regras básicas de posição de agulha e fio - Nomenclatura e sistematização de agulha</t>
   </si>
   <si>
-    <t xml:space="preserve">professor 1</t>
+    <t xml:space="preserve">Helena Nagy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:30 - 13:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teoria do Ponto perfeito e passagem de agulha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sidraiton Melo </t>
   </si>
   <si>
     <t xml:space="preserve">13:00 - 13:30</t>
   </si>
   <si>
-    <t xml:space="preserve">Teoria do Ponto perfeito e passagem de agulha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">professor 2</t>
-  </si>
-  <si>
-    <t>13:30-14:00</t>
-  </si>
-  <si>
     <t xml:space="preserve">Aplicação prática de sutura em videos: Fechamento de cúpula vaginal e miomectomias</t>
   </si>
   <si>
-    <t xml:space="preserve">professor 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:00 - 15:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estação prática</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:00-14:30 </t>
+    <t xml:space="preserve">Guilherme Zanluchi - SP </t>
+  </si>
+  <si>
+    <t xml:space="preserve">13:30 - 15:15
+(01 hora e 
+45 minutos) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estação prática
+Monitores: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">13:30 - 14:05</t>
   </si>
   <si>
     <t xml:space="preserve">Sistematização de 1 grau e acordar as mãos</t>
   </si>
   <si>
-    <t>14:30-15:00</t>
+    <t xml:space="preserve">14:05 - 14:40</t>
   </si>
   <si>
     <t xml:space="preserve">Sistematizaçoes e Cruz de verificaçao</t>
   </si>
   <si>
-    <t xml:space="preserve">15:00 -15:30</t>
+    <t xml:space="preserve">14:40 - 15:15</t>
   </si>
   <si>
     <t xml:space="preserve">O Ponto Perfeito</t>
   </si>
   <si>
-    <t xml:space="preserve">16:00 - 16:30</t>
+    <t xml:space="preserve">15:15 - 15:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:45 - 16:15</t>
   </si>
   <si>
     <t xml:space="preserve">Teoria dos nós: Nó quadrado e semi-chaves</t>
   </si>
   <si>
-    <t xml:space="preserve">16:30 - 17:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Os nós da minha preferência - Aplicação dos nós em cada tipo de tecido e cirurgia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:30 - 19:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:30 - 18:00</t>
+    <t xml:space="preserve">16:15 - 16:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Segurança dos nós </t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:45 - 17:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Os nós da minha preferência - Aplicação dos nós em cada tipo de tecido e cirurgia
+(Triplo / Duplo) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:15 - 19:00
+(01 hora e 
+45 minutos) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:15 - 17:50</t>
   </si>
   <si>
     <t xml:space="preserve">Triplo Duplo - Monomanual e bimanual</t>
   </si>
   <si>
-    <t xml:space="preserve">18:00 - 18:30</t>
+    <t xml:space="preserve">17:50 - 18:25</t>
   </si>
   <si>
     <t xml:space="preserve">Sequência de semi-chaves bloqueantes</t>
   </si>
   <si>
-    <t xml:space="preserve">18:30 - 19:00</t>
+    <t xml:space="preserve">18:25 - 19:00</t>
   </si>
   <si>
     <t xml:space="preserve">Competição - Prêmio </t>
@@ -377,6 +392,7 @@
   <fonts count="9">
     <font>
       <sz val="11.000000"/>
+      <color indexed="64"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -429,7 +445,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -533,8 +549,14 @@
         <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="25">
+  <borders count="26">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -836,6 +858,17 @@
       </bottom>
       <diagonal style="none"/>
     </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -844,7 +877,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="105">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="2" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1135,17 +1168,26 @@
     <xf fontId="4" fillId="18" borderId="24" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf fontId="7" fillId="6" borderId="15" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="7" fillId="6" borderId="16" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="7" fillId="6" borderId="17" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf fontId="8" fillId="7" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="10" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="2" fillId="6" borderId="5" numFmtId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="2" fillId="6" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf fontId="7" fillId="19" borderId="5" numFmtId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="19" borderId="22" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="19" borderId="25" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1174,7 +1216,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>44450</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1409698" cy="314350"/>
+    <xdr:ext cx="1409699" cy="314350"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="14" name="Imagem 13"/>
@@ -1770,12 +1812,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultColWidth="10.26953125" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="10.1796875" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" style="2" width="15.7265625"/>
     <col customWidth="1" min="2" max="2" style="1" width="72.54296875"/>
-    <col customWidth="1" min="3" max="3" style="1" width="29.26953125"/>
-    <col min="4" max="16384" style="1" width="10.26953125"/>
+    <col customWidth="1" min="3" max="3" style="1" width="29.453125"/>
+    <col min="4" max="16384" style="1" width="10.1796875"/>
   </cols>
   <sheetData>
     <row r="1" ht="39.649999999999999" customHeight="1">
@@ -1785,7 +1827,7 @@
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
     </row>
-    <row r="2" s="5" customFormat="1" ht="16.5">
+    <row r="2" s="5" customFormat="1" ht="15.5">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
@@ -2362,7 +2404,7 @@
       </c>
       <c r="D67" s="89"/>
     </row>
-    <row r="68" s="89" customFormat="1" ht="24.75" customHeight="1">
+    <row r="68" s="89" customFormat="1" ht="40" customHeight="1">
       <c r="A68" s="95" t="s">
         <v>95</v>
       </c>
@@ -2379,7 +2421,7 @@
       <c r="B69" s="94" t="s">
         <v>98</v>
       </c>
-      <c r="C69" s="94"/>
+      <c r="C69" s="98"/>
       <c r="D69" s="89"/>
     </row>
     <row r="70" s="89" customFormat="1" ht="24.75" customHeight="1">
@@ -2389,7 +2431,7 @@
       <c r="B70" s="94" t="s">
         <v>100</v>
       </c>
-      <c r="C70" s="94"/>
+      <c r="C70" s="99"/>
       <c r="D70" s="89"/>
     </row>
     <row r="71" s="89" customFormat="1" ht="24.75" customHeight="1">
@@ -2399,14 +2441,14 @@
       <c r="B71" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="C71" s="94"/>
+      <c r="C71" s="100"/>
       <c r="D71" s="89"/>
     </row>
     <row r="72" s="89" customFormat="1" ht="24.75" customHeight="1">
       <c r="A72" s="93" t="s">
-        <v>12</v>
-      </c>
-      <c r="B72" s="98" t="s">
+        <v>103</v>
+      </c>
+      <c r="B72" s="101" t="s">
         <v>13</v>
       </c>
       <c r="C72" s="27"/>
@@ -2414,22 +2456,22 @@
     </row>
     <row r="73" s="89" customFormat="1" ht="24.75" customHeight="1">
       <c r="A73" s="93" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B73" s="94" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C73" s="94" t="s">
         <v>88</v>
       </c>
       <c r="D73" s="89"/>
     </row>
-    <row r="74" s="89" customFormat="1" ht="24.75" customHeight="1">
+    <row r="74" s="89" customFormat="1" ht="24.5" customHeight="1">
       <c r="A74" s="93" t="s">
-        <v>105</v>
-      </c>
-      <c r="B74" s="94" t="s">
         <v>106</v>
+      </c>
+      <c r="B74" s="89" t="s">
+        <v>107</v>
       </c>
       <c r="C74" s="94" t="s">
         <v>91</v>
@@ -2438,54 +2480,58 @@
     </row>
     <row r="75" s="89" customFormat="1" ht="24.75" customHeight="1">
       <c r="A75" s="93" t="s">
-        <v>107</v>
-      </c>
-      <c r="B75" s="86" t="s">
-        <v>96</v>
+        <v>108</v>
+      </c>
+      <c r="B75" s="94" t="s">
+        <v>109</v>
       </c>
       <c r="C75" s="94" t="s">
         <v>94</v>
       </c>
       <c r="D75" s="89"/>
     </row>
-    <row r="76" s="89" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A76" s="93" t="s">
-        <v>108</v>
-      </c>
-      <c r="B76" s="94" t="s">
-        <v>109</v>
-      </c>
-      <c r="C76" s="94"/>
+    <row r="76" s="89" customFormat="1" ht="40" customHeight="1">
+      <c r="A76" s="102" t="s">
+        <v>110</v>
+      </c>
+      <c r="B76" s="103" t="s">
+        <v>96</v>
+      </c>
+      <c r="C76" s="104"/>
       <c r="D76" s="89"/>
     </row>
     <row r="77" s="89" customFormat="1" ht="24.75" customHeight="1">
       <c r="A77" s="93" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B77" s="94" t="s">
-        <v>111</v>
-      </c>
-      <c r="C77" s="94"/>
+        <v>112</v>
+      </c>
+      <c r="C77" s="98"/>
       <c r="D77" s="89"/>
     </row>
     <row r="78" s="89" customFormat="1" ht="24.75" customHeight="1">
       <c r="A78" s="93" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B78" s="94" t="s">
-        <v>113</v>
-      </c>
-      <c r="C78" s="94"/>
+        <v>114</v>
+      </c>
+      <c r="C78" s="99"/>
       <c r="D78" s="89"/>
     </row>
-    <row r="79" s="99" customFormat="1" ht="25" customHeight="1">
-      <c r="A79" s="100"/>
-      <c r="B79" s="101"/>
-      <c r="C79" s="101"/>
-      <c r="D79" s="99"/>
+    <row r="79" s="89" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A79" s="93" t="s">
+        <v>115</v>
+      </c>
+      <c r="B79" s="94" t="s">
+        <v>116</v>
+      </c>
+      <c r="C79" s="100"/>
+      <c r="D79" s="89"/>
     </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="32">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B10:C10"/>
@@ -2514,7 +2560,10 @@
     <mergeCell ref="B60:C60"/>
     <mergeCell ref="B64:C64"/>
     <mergeCell ref="B68:C68"/>
+    <mergeCell ref="C69:C71"/>
     <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="C77:C79"/>
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.39370078740157477" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
